--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118740885</v>
+        <v>118741130</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,47 +1956,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387881</v>
+        <v>387904</v>
       </c>
       <c r="R14" t="n">
-        <v>6610998</v>
+        <v>6611026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118741130</v>
+        <v>118740885</v>
       </c>
       <c r="B15" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,38 +2058,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387904</v>
+        <v>387881</v>
       </c>
       <c r="R15" t="n">
-        <v>6611026</v>
+        <v>6610998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118335253</v>
+        <v>118335255</v>
       </c>
       <c r="B2" t="n">
-        <v>79469</v>
+        <v>90469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387991</v>
+        <v>387867</v>
       </c>
       <c r="R2" t="n">
-        <v>6611130</v>
+        <v>6610985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335255</v>
+        <v>118335256</v>
       </c>
       <c r="B3" t="n">
-        <v>90469</v>
+        <v>90767</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387867</v>
+        <v>387902</v>
       </c>
       <c r="R3" t="n">
-        <v>6610985</v>
+        <v>6610949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118335256</v>
+        <v>118335253</v>
       </c>
       <c r="B5" t="n">
-        <v>90767</v>
+        <v>79469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387902</v>
+        <v>387991</v>
       </c>
       <c r="R5" t="n">
-        <v>6610949</v>
+        <v>6611130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118740511</v>
+        <v>118741130</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,47 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387877</v>
+        <v>387904</v>
       </c>
       <c r="R7" t="n">
-        <v>6610991</v>
+        <v>6611026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118741050</v>
+        <v>118741106</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1331,7 +1322,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1345,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387887</v>
+        <v>387904</v>
       </c>
       <c r="R8" t="n">
-        <v>6611018</v>
+        <v>6611026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118740944</v>
+        <v>118740322</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1442,7 +1433,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1452,14 +1443,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387893</v>
+        <v>387883</v>
       </c>
       <c r="R9" t="n">
-        <v>6611023</v>
+        <v>6610976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118740322</v>
+        <v>118740511</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1553,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1567,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387883</v>
+        <v>387877</v>
       </c>
       <c r="R10" t="n">
-        <v>6610976</v>
+        <v>6610991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118741106</v>
+        <v>118741190</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,47 +1632,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387904</v>
+        <v>387908</v>
       </c>
       <c r="R11" t="n">
-        <v>6611026</v>
+        <v>6611036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118740061</v>
+        <v>118740885</v>
       </c>
       <c r="B12" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1734,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387876</v>
+        <v>387881</v>
       </c>
       <c r="R12" t="n">
-        <v>6610984</v>
+        <v>6610998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118741190</v>
+        <v>118740944</v>
       </c>
       <c r="B13" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,38 +1845,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387908</v>
+        <v>387893</v>
       </c>
       <c r="R13" t="n">
-        <v>6611036</v>
+        <v>6611023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118741130</v>
+        <v>118741050</v>
       </c>
       <c r="B14" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,38 +1956,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387904</v>
+        <v>387887</v>
       </c>
       <c r="R14" t="n">
-        <v>6611026</v>
+        <v>6611018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118740885</v>
+        <v>118740061</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,47 +2067,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387881</v>
+        <v>387876</v>
       </c>
       <c r="R15" t="n">
-        <v>6610998</v>
+        <v>6610984</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118335255</v>
+        <v>118335256</v>
       </c>
       <c r="B2" t="n">
-        <v>90469</v>
+        <v>90767</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387867</v>
+        <v>387902</v>
       </c>
       <c r="R2" t="n">
-        <v>6610985</v>
+        <v>6610949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335256</v>
+        <v>118335255</v>
       </c>
       <c r="B3" t="n">
-        <v>90767</v>
+        <v>90469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387902</v>
+        <v>387867</v>
       </c>
       <c r="R3" t="n">
-        <v>6610949</v>
+        <v>6610985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118741130</v>
+        <v>118740944</v>
       </c>
       <c r="B7" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387904</v>
+        <v>387893</v>
       </c>
       <c r="R7" t="n">
-        <v>6611026</v>
+        <v>6611023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118741106</v>
+        <v>118740322</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1322,7 +1331,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1332,14 +1341,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387904</v>
+        <v>387883</v>
       </c>
       <c r="R8" t="n">
-        <v>6611026</v>
+        <v>6610976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118740322</v>
+        <v>118741190</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,47 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387883</v>
+        <v>387908</v>
       </c>
       <c r="R9" t="n">
-        <v>6610976</v>
+        <v>6611036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118740511</v>
+        <v>118741130</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,47 +1521,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387877</v>
+        <v>387904</v>
       </c>
       <c r="R10" t="n">
-        <v>6610991</v>
+        <v>6611026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118741190</v>
+        <v>118740061</v>
       </c>
       <c r="B11" t="n">
         <v>90469</v>
@@ -1656,14 +1647,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387908</v>
+        <v>387876</v>
       </c>
       <c r="R11" t="n">
-        <v>6611036</v>
+        <v>6610984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1713,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118740885</v>
+        <v>118741050</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1757,7 +1748,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1767,14 +1758,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387881</v>
+        <v>387887</v>
       </c>
       <c r="R12" t="n">
-        <v>6610998</v>
+        <v>6611018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118740944</v>
+        <v>118741106</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1868,7 +1859,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1882,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387893</v>
+        <v>387904</v>
       </c>
       <c r="R13" t="n">
-        <v>6611023</v>
+        <v>6611026</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118741050</v>
+        <v>118740885</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -1979,7 +1970,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1989,14 +1980,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387887</v>
+        <v>387881</v>
       </c>
       <c r="R14" t="n">
-        <v>6611018</v>
+        <v>6610998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118740061</v>
+        <v>118740511</v>
       </c>
       <c r="B15" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,38 +2058,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387876</v>
+        <v>387877</v>
       </c>
       <c r="R15" t="n">
-        <v>6610984</v>
+        <v>6610991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118335256</v>
+        <v>118335255</v>
       </c>
       <c r="B2" t="n">
-        <v>90767</v>
+        <v>90476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387902</v>
+        <v>387867</v>
       </c>
       <c r="R2" t="n">
-        <v>6610949</v>
+        <v>6610985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335255</v>
+        <v>118335252</v>
       </c>
       <c r="B3" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387867</v>
+        <v>387885</v>
       </c>
       <c r="R3" t="n">
-        <v>6610985</v>
+        <v>6611027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118335252</v>
+        <v>118335256</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90774</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387885</v>
+        <v>387902</v>
       </c>
       <c r="R4" t="n">
-        <v>6611027</v>
+        <v>6610949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118335253</v>
+        <v>118335254</v>
       </c>
       <c r="B5" t="n">
-        <v>79469</v>
+        <v>97770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387991</v>
+        <v>387941</v>
       </c>
       <c r="R5" t="n">
-        <v>6611130</v>
+        <v>6611143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118335254</v>
+        <v>118335253</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>79476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387941</v>
+        <v>387991</v>
       </c>
       <c r="R6" t="n">
-        <v>6611143</v>
+        <v>6611130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118740944</v>
+        <v>118741190</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,47 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387893</v>
+        <v>387908</v>
       </c>
       <c r="R7" t="n">
-        <v>6611023</v>
+        <v>6611036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118740322</v>
+        <v>118741130</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,47 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387883</v>
+        <v>387904</v>
       </c>
       <c r="R8" t="n">
-        <v>6610976</v>
+        <v>6611026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118741190</v>
+        <v>118740061</v>
       </c>
       <c r="B9" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,14 +1425,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387908</v>
+        <v>387876</v>
       </c>
       <c r="R9" t="n">
-        <v>6611036</v>
+        <v>6610984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118741130</v>
+        <v>118740511</v>
       </c>
       <c r="B10" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,38 +1503,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387904</v>
+        <v>387877</v>
       </c>
       <c r="R10" t="n">
-        <v>6611026</v>
+        <v>6610991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118740061</v>
+        <v>118740322</v>
       </c>
       <c r="B11" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,38 +1614,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387876</v>
+        <v>387883</v>
       </c>
       <c r="R11" t="n">
-        <v>6610984</v>
+        <v>6610976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118741050</v>
+        <v>118740944</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387887</v>
+        <v>387893</v>
       </c>
       <c r="R12" t="n">
-        <v>6611018</v>
+        <v>6611023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118741106</v>
+        <v>118741050</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387904</v>
+        <v>387887</v>
       </c>
       <c r="R13" t="n">
-        <v>6611026</v>
+        <v>6611018</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1938,7 @@
         <v>118740885</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118740511</v>
+        <v>118741106</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387877</v>
+        <v>387904</v>
       </c>
       <c r="R15" t="n">
-        <v>6610991</v>
+        <v>6611026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118741190</v>
+        <v>118741106</v>
       </c>
       <c r="B7" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387908</v>
+        <v>387904</v>
       </c>
       <c r="R7" t="n">
-        <v>6611036</v>
+        <v>6611026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118741130</v>
+        <v>118741190</v>
       </c>
       <c r="B8" t="n">
         <v>90476</v>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387904</v>
+        <v>387908</v>
       </c>
       <c r="R8" t="n">
-        <v>6611026</v>
+        <v>6611036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118740061</v>
+        <v>118740511</v>
       </c>
       <c r="B9" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1410,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387876</v>
+        <v>387877</v>
       </c>
       <c r="R9" t="n">
-        <v>6610984</v>
+        <v>6610991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118740511</v>
+        <v>118741050</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1526,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1536,14 +1554,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387877</v>
+        <v>387887</v>
       </c>
       <c r="R10" t="n">
-        <v>6610991</v>
+        <v>6611018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118740322</v>
+        <v>118740061</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,47 +1632,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387883</v>
+        <v>387876</v>
       </c>
       <c r="R11" t="n">
-        <v>6610976</v>
+        <v>6610984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118741050</v>
+        <v>118740885</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1859,7 +1868,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1869,14 +1878,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387887</v>
+        <v>387881</v>
       </c>
       <c r="R13" t="n">
-        <v>6611018</v>
+        <v>6610998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118740885</v>
+        <v>118741130</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,47 +1956,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granmossen (Granmossen), Vrm</t>
+          <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387881</v>
+        <v>387904</v>
       </c>
       <c r="R14" t="n">
-        <v>6610998</v>
+        <v>6611026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118741106</v>
+        <v>118740322</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Granmossen (Granmossen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387904</v>
+        <v>387883</v>
       </c>
       <c r="R15" t="n">
-        <v>6611026</v>
+        <v>6610976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2160,7 +2160,7 @@
         <v>121344583</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,6 +2280,108 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123699630</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90966</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>387952</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6611071</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2285,7 +2285,7 @@
         <v>123699630</v>
       </c>
       <c r="B17" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2285,7 +2285,7 @@
         <v>123699630</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2285,7 +2285,7 @@
         <v>123699630</v>
       </c>
       <c r="B17" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2382,6 +2382,552 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123949079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>387930</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6611113</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123949070</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>387926</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6611118</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123946591</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Granmossen, Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>387877</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6611005</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123945944</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Granmossen, Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387867</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6611013</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123946680</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granmossen, Granmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>387875</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6611003</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2928,6 +2928,127 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123976880</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95951</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stockbergen-Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>387949</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6611162</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Björk, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949079</v>
+        <v>123949070</v>
       </c>
       <c r="B18" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,43 +2400,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387930</v>
+        <v>387926</v>
       </c>
       <c r="R18" t="n">
-        <v>6611113</v>
+        <v>6611118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949070</v>
+        <v>123946680</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,38 +2498,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387926</v>
+        <v>387875</v>
       </c>
       <c r="R19" t="n">
-        <v>6611118</v>
+        <v>6611003</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,10 +2597,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123946591</v>
+        <v>123949079</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,47 +2609,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387877</v>
+        <v>387930</v>
       </c>
       <c r="R20" t="n">
-        <v>6611005</v>
+        <v>6611113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
         <v>123945944</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123946680</v>
+        <v>123946591</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387875</v>
+        <v>387877</v>
       </c>
       <c r="R22" t="n">
-        <v>6611003</v>
+        <v>6611005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,7 +2933,7 @@
         <v>123976880</v>
       </c>
       <c r="B23" t="n">
-        <v>95951</v>
+        <v>96332</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949070</v>
+        <v>123945944</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,38 +2396,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387926</v>
+        <v>387867</v>
       </c>
       <c r="R18" t="n">
-        <v>6611118</v>
+        <v>6611013</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123946680</v>
+        <v>123949079</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,47 +2507,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387875</v>
+        <v>387930</v>
       </c>
       <c r="R19" t="n">
-        <v>6611003</v>
+        <v>6611113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949079</v>
+        <v>123946680</v>
       </c>
       <c r="B20" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,47 +2618,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387930</v>
+        <v>387875</v>
       </c>
       <c r="R20" t="n">
-        <v>6611113</v>
+        <v>6611003</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2717,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123945944</v>
+        <v>123946591</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2743,7 +2752,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2757,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387867</v>
+        <v>387877</v>
       </c>
       <c r="R21" t="n">
-        <v>6611013</v>
+        <v>6611005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123946591</v>
+        <v>123949070</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,47 +2840,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387877</v>
+        <v>387926</v>
       </c>
       <c r="R22" t="n">
-        <v>6611005</v>
+        <v>6611118</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123945944</v>
+        <v>123946591</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387867</v>
+        <v>387877</v>
       </c>
       <c r="R18" t="n">
-        <v>6611013</v>
+        <v>6611005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949079</v>
+        <v>123949070</v>
       </c>
       <c r="B19" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,43 +2511,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387930</v>
+        <v>387926</v>
       </c>
       <c r="R19" t="n">
-        <v>6611113</v>
+        <v>6611118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,10 +2597,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123946680</v>
+        <v>123949079</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,47 +2609,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387875</v>
+        <v>387930</v>
       </c>
       <c r="R20" t="n">
-        <v>6611003</v>
+        <v>6611113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123946591</v>
+        <v>123945944</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2752,7 +2743,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2766,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387877</v>
+        <v>387867</v>
       </c>
       <c r="R21" t="n">
-        <v>6611005</v>
+        <v>6611013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949070</v>
+        <v>123946680</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,38 +2831,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387926</v>
+        <v>387875</v>
       </c>
       <c r="R22" t="n">
-        <v>6611118</v>
+        <v>6611003</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123945944</v>
+        <v>123949079</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,47 +2396,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387867</v>
+        <v>387930</v>
       </c>
       <c r="R18" t="n">
-        <v>6611013</v>
+        <v>6611113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123946680</v>
+        <v>123946591</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387875</v>
+        <v>387877</v>
       </c>
       <c r="R19" t="n">
-        <v>6611003</v>
+        <v>6611005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123946591</v>
+        <v>123945944</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387877</v>
+        <v>387867</v>
       </c>
       <c r="R20" t="n">
-        <v>6611005</v>
+        <v>6611013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949079</v>
+        <v>123946680</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,47 +2831,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387930</v>
+        <v>387875</v>
       </c>
       <c r="R22" t="n">
-        <v>6611113</v>
+        <v>6611003</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123946591</v>
+        <v>123949070</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,47 +2507,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387877</v>
+        <v>387926</v>
       </c>
       <c r="R19" t="n">
-        <v>6611005</v>
+        <v>6611118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123949070</v>
+        <v>123946680</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,38 +2720,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387926</v>
+        <v>387875</v>
       </c>
       <c r="R21" t="n">
-        <v>6611118</v>
+        <v>6611003</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123946680</v>
+        <v>123946591</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387875</v>
+        <v>387877</v>
       </c>
       <c r="R22" t="n">
-        <v>6611003</v>
+        <v>6611005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949079</v>
+        <v>123946591</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,47 +2396,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387930</v>
+        <v>387877</v>
       </c>
       <c r="R18" t="n">
-        <v>6611113</v>
+        <v>6611005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949070</v>
+        <v>123945944</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,38 +2507,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387926</v>
+        <v>387867</v>
       </c>
       <c r="R19" t="n">
-        <v>6611118</v>
+        <v>6611013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123945944</v>
+        <v>123946680</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2632,7 +2641,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2646,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387867</v>
+        <v>387875</v>
       </c>
       <c r="R20" t="n">
-        <v>6611013</v>
+        <v>6611003</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123946680</v>
+        <v>123949079</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,47 +2729,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387875</v>
+        <v>387930</v>
       </c>
       <c r="R21" t="n">
-        <v>6611003</v>
+        <v>6611113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123946591</v>
+        <v>123949070</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,47 +2840,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387877</v>
+        <v>387926</v>
       </c>
       <c r="R22" t="n">
-        <v>6611005</v>
+        <v>6611118</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123946591</v>
+        <v>123945944</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387877</v>
+        <v>387867</v>
       </c>
       <c r="R18" t="n">
-        <v>6611005</v>
+        <v>6611013</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123945944</v>
+        <v>123949079</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,47 +2507,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387867</v>
+        <v>387930</v>
       </c>
       <c r="R19" t="n">
-        <v>6611013</v>
+        <v>6611113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123949079</v>
+        <v>123949070</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,43 +2733,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387930</v>
+        <v>387926</v>
       </c>
       <c r="R21" t="n">
-        <v>6611113</v>
+        <v>6611118</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949070</v>
+        <v>123946591</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,38 +2831,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387926</v>
+        <v>387877</v>
       </c>
       <c r="R22" t="n">
-        <v>6611118</v>
+        <v>6611005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123945944</v>
+        <v>123946680</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387867</v>
+        <v>387875</v>
       </c>
       <c r="R18" t="n">
-        <v>6611013</v>
+        <v>6611003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949079</v>
+        <v>123949070</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,43 +2511,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387930</v>
+        <v>387926</v>
       </c>
       <c r="R19" t="n">
-        <v>6611113</v>
+        <v>6611118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,10 +2597,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123946680</v>
+        <v>123949079</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,47 +2609,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granmossen, Granmossen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387875</v>
+        <v>387930</v>
       </c>
       <c r="R20" t="n">
-        <v>6611003</v>
+        <v>6611113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123949070</v>
+        <v>123946591</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,38 +2720,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Granmossen, Granmossen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387926</v>
+        <v>387877</v>
       </c>
       <c r="R21" t="n">
-        <v>6611118</v>
+        <v>6611005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123946591</v>
+        <v>123945944</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387877</v>
+        <v>387867</v>
       </c>
       <c r="R22" t="n">
-        <v>6611005</v>
+        <v>6611013</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,6 +3049,219 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124891064</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>387965</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6611237</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124891069</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105117</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>387965</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6611237</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124891064</v>
+        <v>124891069</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,37 +3063,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
@@ -3162,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124891069</v>
+        <v>124891064</v>
       </c>
       <c r="B25" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3174,28 +3165,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124891069</v>
+        <v>124891064</v>
       </c>
       <c r="B24" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,28 +3063,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>
@@ -3153,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124891064</v>
+        <v>124891069</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,37 +3174,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kusdrågen, Kusdrågen, Vrm</t>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>124891069</v>
       </c>
       <c r="B24" t="n">
-        <v>105117</v>
+        <v>105293</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>124891064</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3262,6 +3262,1750 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125684767</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>387876</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6611020</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125684861</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>387875</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6611017</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125684887</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>387896</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6611020</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125684764</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>387885</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6610990</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125684889</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>387886</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6610993</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125684791</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>387909</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6611050</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125684894</v>
+      </c>
+      <c r="B32" t="n">
+        <v>95122</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>387925</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6611069</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125684795</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>387888</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6611014</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125684793</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>387893</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6611021</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125684888</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>387890</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6611024</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125684792</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>387896</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6611031</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125684765</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>387892</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6610980</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125684890</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>387888</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6610986</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125684859</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>387897</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6610973</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125684766</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>387894</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6610985</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125684794</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>387885</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6611021</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3056,11 +3056,6 @@
       <c r="B24" t="n">
         <v>105293</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>LC</t>
@@ -3158,11 +3153,6 @@
       <c r="B25" t="n">
         <v>98269</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>VU</t>
@@ -3264,15 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684767</v>
+        <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,21 +3282,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387876</v>
+        <v>387890</v>
       </c>
       <c r="R26" t="n">
-        <v>6611020</v>
+        <v>6611024</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3338,12 +3319,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3375,15 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684861</v>
+        <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387875</v>
+        <v>387888</v>
       </c>
       <c r="R27" t="n">
-        <v>6611017</v>
+        <v>6610986</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3445,12 +3421,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3482,37 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684887</v>
+        <v>125684791</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387896</v>
+        <v>387909</v>
       </c>
       <c r="R28" t="n">
-        <v>6611020</v>
+        <v>6611050</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3552,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,15 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684764</v>
+        <v>125684889</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3622,21 +3588,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387885</v>
+        <v>387886</v>
       </c>
       <c r="R29" t="n">
-        <v>6610990</v>
+        <v>6610993</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3663,12 +3625,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3700,15 +3662,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125684889</v>
+        <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,17 +3690,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387886</v>
+        <v>387885</v>
       </c>
       <c r="R30" t="n">
-        <v>6610993</v>
+        <v>6610990</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3770,12 +3731,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3807,15 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684791</v>
+        <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>92098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>2383</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387909</v>
+        <v>387925</v>
       </c>
       <c r="R31" t="n">
-        <v>6611050</v>
+        <v>6611069</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3877,17 +3833,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,37 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>95122</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R32" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3984,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4021,15 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125684795</v>
+        <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4065,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387888</v>
+        <v>387892</v>
       </c>
       <c r="R33" t="n">
-        <v>6611014</v>
+        <v>6610980</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4095,12 +4041,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4135,12 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4243,15 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125684888</v>
+        <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387890</v>
+        <v>387896</v>
       </c>
       <c r="R35" t="n">
-        <v>6611024</v>
+        <v>6611020</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4350,15 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125684792</v>
+        <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4316,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4394,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387896</v>
+        <v>387894</v>
       </c>
       <c r="R36" t="n">
-        <v>6611031</v>
+        <v>6610985</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4424,12 +4355,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4461,15 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125684765</v>
+        <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,7 +4422,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4505,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387892</v>
+        <v>387896</v>
       </c>
       <c r="R37" t="n">
-        <v>6610980</v>
+        <v>6611031</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4535,12 +4461,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4572,15 +4498,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125684890</v>
+        <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4612,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387888</v>
+        <v>387897</v>
       </c>
       <c r="R38" t="n">
-        <v>6610986</v>
+        <v>6610973</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4642,12 +4563,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4679,15 +4600,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125684859</v>
+        <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,17 +4628,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387897</v>
+        <v>387876</v>
       </c>
       <c r="R39" t="n">
-        <v>6610973</v>
+        <v>6611020</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4749,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4786,15 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125684766</v>
+        <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4736,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4830,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387894</v>
+        <v>387885</v>
       </c>
       <c r="R40" t="n">
-        <v>6610985</v>
+        <v>6611021</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4860,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4897,15 +4812,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125684794</v>
+        <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4842,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4941,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387885</v>
+        <v>387888</v>
       </c>
       <c r="R41" t="n">
-        <v>6611021</v>
+        <v>6611014</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B28" t="n">
-        <v>92152</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R28" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>92159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R29" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>95176</v>
+        <v>95183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125684889</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>125684791</v>
       </c>
       <c r="B29" t="n">
-        <v>92159</v>
+        <v>92163</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>95183</v>
+        <v>95186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>92167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R28" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B29" t="n">
-        <v>92163</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R29" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B31" t="n">
-        <v>95186</v>
+        <v>98338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R31" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>95190</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R32" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>98338</v>
+        <v>95190</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R31" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>95190</v>
+        <v>98338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R32" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3254,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684888</v>
+        <v>125684890</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387890</v>
+        <v>387888</v>
       </c>
       <c r="R26" t="n">
-        <v>6611024</v>
+        <v>6610986</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684890</v>
+        <v>125684888</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387888</v>
+        <v>387890</v>
       </c>
       <c r="R27" t="n">
-        <v>6610986</v>
+        <v>6611024</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B28" t="n">
-        <v>92167</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R28" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>92167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R29" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B31" t="n">
-        <v>95190</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R31" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B32" t="n">
-        <v>98338</v>
+        <v>95191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R32" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125684767</v>
+        <v>125684794</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387876</v>
+        <v>387885</v>
       </c>
       <c r="R39" t="n">
-        <v>6611020</v>
+        <v>6611021</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125684794</v>
+        <v>125684767</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387885</v>
+        <v>387876</v>
       </c>
       <c r="R40" t="n">
-        <v>6611021</v>
+        <v>6611020</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>95191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R31" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>95191</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R32" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684890</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684888</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125684889</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>125684791</v>
       </c>
       <c r="B29" t="n">
-        <v>92167</v>
+        <v>92169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>95191</v>
+        <v>95193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684794</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684767</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3254,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684890</v>
+        <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387888</v>
+        <v>387890</v>
       </c>
       <c r="R26" t="n">
-        <v>6610986</v>
+        <v>6611024</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684888</v>
+        <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387890</v>
+        <v>387888</v>
       </c>
       <c r="R27" t="n">
-        <v>6611024</v>
+        <v>6610986</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>92171</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R28" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B29" t="n">
-        <v>92169</v>
+        <v>98343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R29" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B31" t="n">
-        <v>95193</v>
+        <v>98343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R31" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>95195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R32" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125684794</v>
+        <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387885</v>
+        <v>387876</v>
       </c>
       <c r="R39" t="n">
-        <v>6611021</v>
+        <v>6611020</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125684767</v>
+        <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387876</v>
+        <v>387885</v>
       </c>
       <c r="R40" t="n">
-        <v>6611020</v>
+        <v>6611021</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>98343</v>
+        <v>95195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R31" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>95195</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R32" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125684791</v>
       </c>
       <c r="B28" t="n">
-        <v>92171</v>
+        <v>92173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>125684889</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>95195</v>
+        <v>95197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125684767</v>
+        <v>125684794</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387876</v>
+        <v>387885</v>
       </c>
       <c r="R39" t="n">
-        <v>6611020</v>
+        <v>6611021</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125684794</v>
+        <v>125684767</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387885</v>
+        <v>387876</v>
       </c>
       <c r="R40" t="n">
-        <v>6611021</v>
+        <v>6611020</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -4600,7 +4600,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125684794</v>
+        <v>125684767</v>
       </c>
       <c r="B39" t="n">
         <v>98345</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387885</v>
+        <v>387876</v>
       </c>
       <c r="R39" t="n">
-        <v>6611021</v>
+        <v>6611020</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125684767</v>
+        <v>125684794</v>
       </c>
       <c r="B40" t="n">
         <v>98345</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387876</v>
+        <v>387885</v>
       </c>
       <c r="R40" t="n">
-        <v>6611020</v>
+        <v>6611021</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3254,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684888</v>
+        <v>125684890</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387890</v>
+        <v>387888</v>
       </c>
       <c r="R26" t="n">
-        <v>6611024</v>
+        <v>6610986</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684890</v>
+        <v>125684888</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387888</v>
+        <v>387890</v>
       </c>
       <c r="R27" t="n">
-        <v>6610986</v>
+        <v>6611024</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B28" t="n">
-        <v>92173</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R28" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>92177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R29" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B31" t="n">
-        <v>95197</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R31" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>95201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R32" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684890</v>
+        <v>125684888</v>
       </c>
       <c r="B26" t="n">
         <v>98349</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387888</v>
+        <v>387890</v>
       </c>
       <c r="R26" t="n">
-        <v>6610986</v>
+        <v>6611024</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684888</v>
+        <v>125684890</v>
       </c>
       <c r="B27" t="n">
         <v>98349</v>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387890</v>
+        <v>387888</v>
       </c>
       <c r="R27" t="n">
-        <v>6611024</v>
+        <v>6610986</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>125684888</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125684890</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,32 +3458,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684889</v>
+        <v>125684791</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>92177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387886</v>
+        <v>387909</v>
       </c>
       <c r="R28" t="n">
-        <v>6610993</v>
+        <v>6611050</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, fjolårsfruktkroppar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,32 +3560,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125684791</v>
+        <v>125684889</v>
       </c>
       <c r="B29" t="n">
-        <v>92177</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387909</v>
+        <v>387886</v>
       </c>
       <c r="R29" t="n">
-        <v>6611050</v>
+        <v>6610993</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Stockbergen, fjolårsfruktkroppar</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
         <v>125684764</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125684861</v>
+        <v>125684894</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>95204</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2383</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387875</v>
+        <v>387925</v>
       </c>
       <c r="R31" t="n">
-        <v>6611017</v>
+        <v>6611069</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3870,32 +3870,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125684894</v>
+        <v>125684861</v>
       </c>
       <c r="B32" t="n">
-        <v>95201</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387925</v>
+        <v>387875</v>
       </c>
       <c r="R32" t="n">
-        <v>6611069</v>
+        <v>6611017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>125684765</v>
       </c>
       <c r="B33" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>125684793</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>125684887</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>125684766</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>125684792</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>125684859</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>125684767</v>
       </c>
       <c r="B39" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>125684794</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125684795</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,121 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129895272</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogsbergsstjärnet, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387966</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611237</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>S-Arv-0869</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,121 +1516,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>129895272</v>
-      </c>
-      <c r="B10" t="n">
-        <v>98785</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skogsbergsstjärnet, SV om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>387966</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6611237</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>S-Arv-0869</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,121 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129895272</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogsbergsstjärnet, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387966</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611237</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>S-Arv-0869</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,121 +1516,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>129895272</v>
-      </c>
-      <c r="B10" t="n">
-        <v>98833</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skogsbergsstjärnet, SV om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>387966</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6611237</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>S-Arv-0869</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23087-2024 artfynd.xlsx
+++ b/artfynd/A 23087-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118335254</v>
+        <v>123976880</v>
       </c>
       <c r="B2" t="n">
-        <v>97770</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kusdrågen, Arvika, Vrm</t>
+          <t>Stockbergen-Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387941</v>
+        <v>387949</v>
       </c>
       <c r="R2" t="n">
-        <v>6611143</v>
+        <v>6611162</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,66 +760,76 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk, Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335253</v>
+        <v>123699630</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kusdrågen, Arvika, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387991</v>
+        <v>387952</v>
       </c>
       <c r="R3" t="n">
-        <v>6611130</v>
+        <v>6611071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699630</v>
+        <v>123949070</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387952</v>
+        <v>387926</v>
       </c>
       <c r="R4" t="n">
-        <v>6611071</v>
+        <v>6611118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,60 +978,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Alexander Singer, Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123949070</v>
+        <v>125684894</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387926</v>
+        <v>387925</v>
       </c>
       <c r="R5" t="n">
-        <v>6611118</v>
+        <v>6611069</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1050,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,71 +1075,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer, Anton Björk</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123949079</v>
+        <v>118335253</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Kusdrågen, Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387930</v>
+        <v>387991</v>
       </c>
       <c r="R6" t="n">
-        <v>6611113</v>
+        <v>6611130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,27 +1172,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer, Anton Björk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123976880</v>
+        <v>123949079</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,41 +1195,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockbergen-Glansbergen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387949</v>
+        <v>387930</v>
       </c>
       <c r="R7" t="n">
-        <v>6611162</v>
+        <v>6611113</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,41 +1274,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk, Alexander Singer</t>
+          <t>Alexander Singer, Anton Björk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891069</v>
+        <v>118335254</v>
       </c>
       <c r="B8" t="n">
-        <v>105293</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,34 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kusdrågen, Kusdrågen, Vrm</t>
+          <t>Kusdrågen, Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387965</v>
+        <v>387941</v>
       </c>
       <c r="R8" t="n">
-        <v>6611237</v>
+        <v>6611143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1355,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1415,7 +1390,7 @@
         <v>124891064</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,6 +1490,205 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124891069</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387965</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611237</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125684777</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>387923</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611198</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
